--- a/completed/sonogashira_10.1039.B915669K.xlsx
+++ b/completed/sonogashira_10.1039.B915669K.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/completed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF55BC6-A078-C54A-8ADE-39346D8A1C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A00D05-7828-454D-85E7-B40BC764635E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11900" yWindow="500" windowWidth="23940" windowHeight="15360" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
   </bookViews>
@@ -265,7 +265,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -342,6 +342,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -357,11 +370,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -700,31 +713,32 @@
   <dimension ref="A2:V69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="11.1640625" style="4"/>
     <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.1640625" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" customWidth="1"/>
     <col min="6" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
+      <c r="A3" s="13"/>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -744,7 +758,7 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
+      <c r="A4" s="13"/>
       <c r="E4" t="s">
         <v>16</v>
       </c>
@@ -753,20 +767,20 @@
       </c>
     </row>
     <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="8"/>
@@ -781,21 +795,21 @@
       <c r="P5"/>
     </row>
     <row r="6" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
@@ -815,7 +829,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -845,22 +859,12 @@
       </c>
     </row>
     <row r="9" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
+      <c r="A10" s="13"/>
       <c r="B10" t="s">
         <v>24</v>
       </c>
@@ -890,7 +894,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
+      <c r="A11" s="13"/>
       <c r="B11" t="s">
         <v>20</v>
       </c>
@@ -920,7 +924,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
+      <c r="A12" s="13"/>
       <c r="B12" t="s">
         <v>24</v>
       </c>
@@ -950,7 +954,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
+      <c r="A13" s="13"/>
       <c r="B13" t="s">
         <v>20</v>
       </c>
@@ -980,7 +984,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
+      <c r="A14" s="13"/>
       <c r="B14" t="s">
         <v>24</v>
       </c>
@@ -1010,7 +1014,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
+      <c r="A15" s="13"/>
       <c r="B15" t="s">
         <v>20</v>
       </c>
@@ -1040,7 +1044,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
+      <c r="A16" s="13"/>
       <c r="B16" t="s">
         <v>24</v>
       </c>
@@ -1070,7 +1074,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
+      <c r="A17" s="13"/>
       <c r="B17" t="s">
         <v>20</v>
       </c>
@@ -1100,7 +1104,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
+      <c r="A18" s="13"/>
       <c r="B18" t="s">
         <v>24</v>
       </c>
@@ -1130,7 +1134,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A19" s="9"/>
+      <c r="A19" s="13"/>
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1160,7 +1164,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A20" s="9"/>
+      <c r="A20" s="13"/>
       <c r="B20" t="s">
         <v>24</v>
       </c>
@@ -1190,7 +1194,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
+      <c r="A21" s="13"/>
       <c r="B21" t="s">
         <v>20</v>
       </c>
@@ -1220,7 +1224,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
+      <c r="A22" s="13"/>
       <c r="B22" t="s">
         <v>24</v>
       </c>
@@ -1250,7 +1254,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A23" s="9"/>
+      <c r="A23" s="13"/>
       <c r="B23" t="s">
         <v>20</v>
       </c>
@@ -1280,7 +1284,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A24" s="9"/>
+      <c r="A24" s="13"/>
       <c r="B24" t="s">
         <v>24</v>
       </c>
@@ -1310,7 +1314,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
+      <c r="A25" s="13"/>
       <c r="B25" t="s">
         <v>20</v>
       </c>
@@ -1340,7 +1344,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
+      <c r="A26" s="13"/>
       <c r="B26" t="s">
         <v>24</v>
       </c>
@@ -1370,7 +1374,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
+      <c r="A27" s="13"/>
       <c r="B27" t="s">
         <v>20</v>
       </c>
@@ -1402,7 +1406,7 @@
       <c r="V27" s="4"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
+      <c r="A28" s="13"/>
       <c r="B28" t="s">
         <v>24</v>
       </c>
@@ -1434,7 +1438,7 @@
       <c r="V28" s="4"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A29" s="9"/>
+      <c r="A29" s="13"/>
       <c r="B29" t="s">
         <v>20</v>
       </c>
@@ -1466,7 +1470,7 @@
       <c r="V29" s="4"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A30" s="9"/>
+      <c r="A30" s="13"/>
       <c r="B30" t="s">
         <v>24</v>
       </c>
@@ -1498,7 +1502,7 @@
       <c r="V30" s="4"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
+      <c r="A31" s="13"/>
       <c r="B31" t="s">
         <v>20</v>
       </c>
@@ -1530,7 +1534,7 @@
       <c r="V31" s="4"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
+      <c r="A32" s="13"/>
       <c r="B32" t="s">
         <v>24</v>
       </c>
@@ -1562,7 +1566,7 @@
       <c r="V32" s="4"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
+      <c r="A33" s="13"/>
       <c r="B33" t="s">
         <v>20</v>
       </c>
@@ -1594,7 +1598,7 @@
       <c r="V33" s="4"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
+      <c r="A34" s="13"/>
       <c r="B34" t="s">
         <v>24</v>
       </c>
@@ -1626,7 +1630,7 @@
       <c r="V34" s="4"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="9"/>
+      <c r="A35" s="13"/>
       <c r="B35" t="s">
         <v>20</v>
       </c>
@@ -1658,7 +1662,7 @@
       <c r="V35" s="4"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="9"/>
+      <c r="A36" s="13"/>
       <c r="B36" t="s">
         <v>24</v>
       </c>
@@ -1690,7 +1694,7 @@
       <c r="V36" s="4"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
+      <c r="A37" s="13"/>
       <c r="B37" t="s">
         <v>20</v>
       </c>
@@ -1722,7 +1726,7 @@
       <c r="V37" s="4"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="9"/>
+      <c r="A38" s="13"/>
       <c r="B38" t="s">
         <v>24</v>
       </c>
@@ -1754,7 +1758,7 @@
       <c r="V38" s="4"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="9"/>
+      <c r="A39" s="13"/>
       <c r="B39" t="s">
         <v>20</v>
       </c>
@@ -1786,7 +1790,7 @@
       <c r="V39" s="4"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
+      <c r="A40" s="13"/>
       <c r="B40" t="s">
         <v>24</v>
       </c>
@@ -1818,7 +1822,7 @@
       <c r="V40" s="4"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="9"/>
+      <c r="A41" s="13"/>
       <c r="B41" t="s">
         <v>20</v>
       </c>
@@ -1850,7 +1854,7 @@
       <c r="V41" s="4"/>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A42" s="9"/>
+      <c r="A42" s="13"/>
       <c r="B42" t="s">
         <v>24</v>
       </c>
@@ -1882,7 +1886,7 @@
       <c r="V42" s="4"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A43" s="9"/>
+      <c r="A43" s="13"/>
       <c r="B43" t="s">
         <v>24</v>
       </c>
@@ -1914,7 +1918,7 @@
       <c r="V43" s="4"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A44" s="9"/>
+      <c r="A44" s="13"/>
       <c r="B44" t="s">
         <v>24</v>
       </c>
@@ -1946,7 +1950,7 @@
       <c r="V44" s="4"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A45" s="9"/>
+      <c r="A45" s="13"/>
       <c r="B45" t="s">
         <v>24</v>
       </c>
@@ -1978,7 +1982,7 @@
       <c r="V45" s="4"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A46" s="9"/>
+      <c r="A46" s="13"/>
       <c r="B46" t="s">
         <v>24</v>
       </c>
@@ -2010,7 +2014,7 @@
       <c r="V46" s="4"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A47" s="9"/>
+      <c r="A47" s="13"/>
       <c r="B47" t="s">
         <v>24</v>
       </c>
@@ -2042,7 +2046,7 @@
       <c r="V47" s="4"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A48" s="9"/>
+      <c r="A48" s="13"/>
       <c r="B48" t="s">
         <v>24</v>
       </c>
@@ -2074,7 +2078,7 @@
       <c r="V48" s="4"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A49" s="9"/>
+      <c r="A49" s="13"/>
       <c r="B49" t="s">
         <v>24</v>
       </c>
@@ -2106,7 +2110,7 @@
       <c r="V49" s="4"/>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A50" s="9"/>
+      <c r="A50" s="13"/>
       <c r="B50" t="s">
         <v>24</v>
       </c>
@@ -2138,7 +2142,7 @@
       <c r="V50" s="4"/>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A51" s="9"/>
+      <c r="A51" s="13"/>
       <c r="B51" t="s">
         <v>24</v>
       </c>
@@ -2170,7 +2174,7 @@
       <c r="V51" s="4"/>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A52" s="9"/>
+      <c r="A52" s="13"/>
       <c r="B52" t="s">
         <v>24</v>
       </c>
@@ -2202,7 +2206,7 @@
       <c r="V52" s="4"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A53" s="9"/>
+      <c r="A53" s="13"/>
       <c r="B53" t="s">
         <v>24</v>
       </c>
@@ -2234,7 +2238,7 @@
       <c r="V53" s="4"/>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A54" s="9"/>
+      <c r="A54" s="13"/>
       <c r="B54" t="s">
         <v>24</v>
       </c>
@@ -2266,7 +2270,7 @@
       <c r="V54" s="4"/>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A55" s="9"/>
+      <c r="A55" s="13"/>
       <c r="B55" t="s">
         <v>24</v>
       </c>
@@ -2298,7 +2302,7 @@
       <c r="V55" s="4"/>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A56" s="9"/>
+      <c r="A56" s="13"/>
       <c r="B56" t="s">
         <v>24</v>
       </c>
@@ -2321,7 +2325,7 @@
       <c r="V56" s="4"/>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A57" s="9"/>
+      <c r="A57" s="13"/>
       <c r="B57" t="s">
         <v>24</v>
       </c>
@@ -2353,7 +2357,7 @@
       <c r="V57" s="4"/>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A58" s="9"/>
+      <c r="A58" s="13"/>
       <c r="B58" t="s">
         <v>24</v>
       </c>
@@ -2385,7 +2389,7 @@
       <c r="V58" s="4"/>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A59" s="9"/>
+      <c r="A59" s="13"/>
       <c r="B59" t="s">
         <v>24</v>
       </c>
@@ -2417,7 +2421,7 @@
       <c r="V59" s="4"/>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A60" s="9"/>
+      <c r="A60" s="13"/>
       <c r="B60" t="s">
         <v>24</v>
       </c>
@@ -2449,7 +2453,7 @@
       <c r="V60" s="4"/>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A61" s="9"/>
+      <c r="A61" s="13"/>
       <c r="B61" t="s">
         <v>24</v>
       </c>
@@ -2559,7 +2563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
         <v>24</v>
       </c>
@@ -2588,7 +2592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>24</v>
       </c>
@@ -2617,7 +2621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
         <v>24</v>
       </c>
@@ -2646,7 +2650,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
         <v>24</v>
       </c>
@@ -2675,8 +2679,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A69" s="4"/>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
         <v>24</v>
       </c>
